--- a/inst/extdata/ega_full_template_v3.xlsx
+++ b/inst/extdata/ega_full_template_v3.xlsx
@@ -616,7 +616,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="458">
   <si>
     <t xml:space="preserve">Please read the instructions carefully to avoid submission errors</t>
   </si>
@@ -967,6 +967,51 @@
   </si>
   <si>
     <t xml:space="preserve">Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status_types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">study_types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biological_sex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">case_controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">platform_models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">library_layouts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">library_strategies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">library_sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">library_selections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run_file_types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis_types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">experiment_types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">genomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chromosomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataset_types</t>
   </si>
   <si>
     <t xml:space="preserve">open</t>
@@ -2786,17 +2831,17 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s">
+      <c r="A75" s="2" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2961,25 +3006,25 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$K1:$K3</xm:f>
+            <xm:f>'Select Input Data'!$K$2:$K$4</xm:f>
           </x14:formula1>
           <xm:sqref>B5:B5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$L1:$L8</xm:f>
+            <xm:f>'Select Input Data'!$L$2:$L$9</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B6</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$M1:$M29</xm:f>
+            <xm:f>'Select Input Data'!$M$2:$M$30</xm:f>
           </x14:formula1>
           <xm:sqref>B7:B7</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$N1:$N74</xm:f>
+            <xm:f>'Select Input Data'!$N$2:$N$75</xm:f>
           </x14:formula1>
           <xm:sqref>B10:B10</xm:sqref>
         </x14:dataValidation>
@@ -3080,7 +3125,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Aliases'!$D$2:$D$1000</xm:f>
+            <xm:f>'Aliases'!$E$2:$E$1000</xm:f>
           </x14:formula1>
           <xm:sqref>B7:B7</xm:sqref>
         </x14:dataValidation>
@@ -3092,7 +3137,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$O1:$O14</xm:f>
+            <xm:f>'Select Input Data'!$O$2:$O$15</xm:f>
           </x14:formula1>
           <xm:sqref>B5:B5</xm:sqref>
         </x14:dataValidation>
@@ -3241,54 +3286,54 @@
         <v>130</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M2" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="O2" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="3">
@@ -3307,446 +3352,466 @@
       <c r="E3" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="6" t="s">
+        <v>151</v>
+      </c>
       <c r="G3" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="K4" s="6"/>
+        <v>96</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>169</v>
+      </c>
       <c r="L4" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6"/>
+      <c r="A5" s="6" t="s">
+        <v>173</v>
+      </c>
       <c r="B5" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+        <v>174</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>176</v>
+      </c>
       <c r="E5" s="6" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="K5" s="6"/>
       <c r="L5" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+      <c r="L9" s="6" t="s">
+        <v>221</v>
+      </c>
       <c r="M9" s="6" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="H10" s="6"/>
+        <v>227</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>228</v>
+      </c>
       <c r="I10" s="6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="J12" s="6"/>
+        <v>245</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>246</v>
+      </c>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+      <c r="B15" s="6" t="s">
+        <v>264</v>
+      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="O15" s="6"/>
+        <v>269</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6"/>
@@ -3754,24 +3819,24 @@
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="O16" s="6"/>
     </row>
@@ -3781,24 +3846,24 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="O17" s="6"/>
     </row>
@@ -3808,24 +3873,24 @@
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="6" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="O18" s="6"/>
     </row>
@@ -3835,24 +3900,24 @@
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="O19" s="6"/>
     </row>
@@ -3862,24 +3927,24 @@
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="6" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="O20" s="6"/>
     </row>
@@ -3889,24 +3954,24 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="O21" s="6"/>
     </row>
@@ -3916,24 +3981,24 @@
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="O22" s="6"/>
     </row>
@@ -3943,24 +4008,24 @@
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="O23" s="6"/>
     </row>
@@ -3970,24 +4035,24 @@
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="6" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="O24" s="6"/>
     </row>
@@ -3997,24 +4062,24 @@
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="6" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="O25" s="6"/>
     </row>
@@ -4024,24 +4089,24 @@
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="6" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="O26" s="6"/>
     </row>
@@ -4051,24 +4116,24 @@
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="O27" s="6"/>
     </row>
@@ -4078,24 +4143,24 @@
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="6" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="O28" s="6"/>
     </row>
@@ -4105,24 +4170,24 @@
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="O29" s="6"/>
     </row>
@@ -4132,22 +4197,24 @@
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="6" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
+      <c r="M30" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="N30" s="6" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="O30" s="6"/>
     </row>
@@ -4157,22 +4224,22 @@
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="O31" s="6"/>
     </row>
@@ -4182,20 +4249,22 @@
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
+      <c r="I32" s="6" t="s">
+        <v>351</v>
+      </c>
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="O32" s="6"/>
     </row>
@@ -4205,11 +4274,11 @@
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
@@ -4218,7 +4287,7 @@
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="O33" s="6"/>
     </row>
@@ -4228,11 +4297,11 @@
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
@@ -4241,7 +4310,7 @@
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="O34" s="6"/>
     </row>
@@ -4251,11 +4320,11 @@
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
@@ -4264,7 +4333,7 @@
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="O35" s="6"/>
     </row>
@@ -4274,11 +4343,11 @@
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
@@ -4287,7 +4356,7 @@
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="O36" s="6"/>
     </row>
@@ -4297,11 +4366,11 @@
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
@@ -4310,7 +4379,7 @@
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
       <c r="N37" s="6" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="O37" s="6"/>
     </row>
@@ -4320,11 +4389,11 @@
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
@@ -4333,7 +4402,7 @@
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
       <c r="N38" s="6" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="O38" s="6"/>
     </row>
@@ -4343,11 +4412,11 @@
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="6" t="s">
-        <v>213</v>
+        <v>372</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
@@ -4356,7 +4425,7 @@
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="O39" s="6"/>
     </row>
@@ -4366,11 +4435,11 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="6" t="s">
-        <v>362</v>
+        <v>228</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
@@ -4379,7 +4448,7 @@
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="O40" s="6"/>
     </row>
@@ -4389,11 +4458,11 @@
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="6" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
@@ -4402,7 +4471,7 @@
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="O41" s="6"/>
     </row>
@@ -4412,10 +4481,12 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
+      <c r="G42" s="6" t="s">
+        <v>380</v>
+      </c>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
@@ -4423,7 +4494,7 @@
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="O42" s="6"/>
     </row>
@@ -4433,7 +4504,7 @@
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
@@ -4444,7 +4515,7 @@
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="O43" s="6"/>
     </row>
@@ -4454,7 +4525,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
@@ -4465,7 +4536,7 @@
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="O44" s="6"/>
     </row>
@@ -4475,7 +4546,7 @@
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
@@ -4486,7 +4557,7 @@
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="O45" s="6"/>
     </row>
@@ -4496,7 +4567,7 @@
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
@@ -4507,7 +4578,7 @@
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="O46" s="6"/>
     </row>
@@ -4517,7 +4588,7 @@
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
@@ -4528,7 +4599,7 @@
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="O47" s="6"/>
     </row>
@@ -4538,7 +4609,7 @@
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
@@ -4549,7 +4620,7 @@
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="O48" s="6"/>
     </row>
@@ -4559,7 +4630,7 @@
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
@@ -4570,7 +4641,7 @@
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="O49" s="6"/>
     </row>
@@ -4580,7 +4651,7 @@
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
@@ -4591,7 +4662,7 @@
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="O50" s="6"/>
     </row>
@@ -4601,7 +4672,7 @@
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
@@ -4612,7 +4683,7 @@
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="O51" s="6"/>
     </row>
@@ -4622,7 +4693,7 @@
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
@@ -4633,7 +4704,7 @@
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="O52" s="6"/>
     </row>
@@ -4643,7 +4714,7 @@
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
@@ -4654,7 +4725,7 @@
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="O53" s="6"/>
     </row>
@@ -4664,7 +4735,7 @@
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
       <c r="E54" s="6" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
@@ -4675,7 +4746,7 @@
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="O54" s="6"/>
     </row>
@@ -4685,7 +4756,7 @@
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
@@ -4696,7 +4767,7 @@
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O55" s="6"/>
     </row>
@@ -4706,7 +4777,7 @@
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
@@ -4717,7 +4788,7 @@
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="O56" s="6"/>
     </row>
@@ -4727,7 +4798,7 @@
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
@@ -4738,7 +4809,7 @@
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="O57" s="6"/>
     </row>
@@ -4748,7 +4819,7 @@
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
@@ -4759,7 +4830,7 @@
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="O58" s="6"/>
     </row>
@@ -4769,7 +4840,7 @@
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
@@ -4780,7 +4851,7 @@
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="O59" s="6"/>
     </row>
@@ -4790,7 +4861,7 @@
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
@@ -4801,7 +4872,7 @@
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="O60" s="6"/>
     </row>
@@ -4811,7 +4882,7 @@
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
@@ -4822,7 +4893,7 @@
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="O61" s="6"/>
     </row>
@@ -4832,7 +4903,7 @@
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="6" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
@@ -4843,7 +4914,7 @@
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
       <c r="N62" s="6" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="O62" s="6"/>
     </row>
@@ -4853,7 +4924,7 @@
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
@@ -4864,7 +4935,7 @@
       <c r="L63" s="6"/>
       <c r="M63" s="6"/>
       <c r="N63" s="6" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="O63" s="6"/>
     </row>
@@ -4874,7 +4945,7 @@
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
@@ -4885,7 +4956,7 @@
       <c r="L64" s="6"/>
       <c r="M64" s="6"/>
       <c r="N64" s="6" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="O64" s="6"/>
     </row>
@@ -4895,7 +4966,7 @@
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
@@ -4906,7 +4977,7 @@
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="O65" s="6"/>
     </row>
@@ -4916,7 +4987,7 @@
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
@@ -4927,7 +4998,7 @@
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="O66" s="6"/>
     </row>
@@ -4937,7 +5008,7 @@
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
@@ -4948,7 +5019,7 @@
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="O67" s="6"/>
     </row>
@@ -4958,7 +5029,7 @@
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
@@ -4969,7 +5040,7 @@
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="O68" s="6"/>
     </row>
@@ -4979,7 +5050,7 @@
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
       <c r="E69" s="6" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
@@ -4990,7 +5061,7 @@
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
       <c r="N69" s="6" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="O69" s="6"/>
     </row>
@@ -5000,7 +5071,7 @@
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
       <c r="E70" s="6" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
@@ -5011,7 +5082,7 @@
       <c r="L70" s="6"/>
       <c r="M70" s="6"/>
       <c r="N70" s="6" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="O70" s="6"/>
     </row>
@@ -5021,7 +5092,7 @@
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
@@ -5032,7 +5103,7 @@
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
       <c r="N71" s="6" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="O71" s="6"/>
     </row>
@@ -5042,7 +5113,7 @@
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
       <c r="E72" s="6" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
@@ -5053,7 +5124,7 @@
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
       <c r="N72" s="6" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="O72" s="6"/>
     </row>
@@ -5063,7 +5134,7 @@
       <c r="C73" s="6"/>
       <c r="D73" s="6"/>
       <c r="E73" s="6" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
@@ -5074,7 +5145,7 @@
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="O73" s="6"/>
     </row>
@@ -5084,7 +5155,7 @@
       <c r="C74" s="6"/>
       <c r="D74" s="6"/>
       <c r="E74" s="6" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
@@ -5095,7 +5166,7 @@
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="O74" s="6"/>
     </row>
@@ -5105,7 +5176,7 @@
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
       <c r="E75" s="6" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
@@ -5115,7 +5186,9 @@
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
-      <c r="N75" s="6"/>
+      <c r="N75" s="6" t="s">
+        <v>447</v>
+      </c>
       <c r="O75" s="6"/>
     </row>
     <row r="76">
@@ -5124,7 +5197,7 @@
       <c r="C76" s="6"/>
       <c r="D76" s="6"/>
       <c r="E76" s="6" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
@@ -5143,7 +5216,7 @@
       <c r="C77" s="6"/>
       <c r="D77" s="6"/>
       <c r="E77" s="6" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
@@ -5162,7 +5235,7 @@
       <c r="C78" s="6"/>
       <c r="D78" s="6"/>
       <c r="E78" s="6" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
@@ -5181,7 +5254,7 @@
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
       <c r="E79" s="6" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
@@ -5200,7 +5273,7 @@
       <c r="C80" s="6"/>
       <c r="D80" s="6"/>
       <c r="E80" s="6" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
@@ -5219,7 +5292,7 @@
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
       <c r="E81" s="6" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
@@ -5238,7 +5311,7 @@
       <c r="C82" s="6"/>
       <c r="D82" s="6"/>
       <c r="E82" s="6" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
@@ -5257,7 +5330,7 @@
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
       <c r="E83" s="6" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
@@ -5276,7 +5349,7 @@
       <c r="C84" s="6"/>
       <c r="D84" s="6"/>
       <c r="E84" s="6" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
@@ -5288,6 +5361,25 @@
       <c r="M84" s="6"/>
       <c r="N84" s="6"/>
       <c r="O84" s="6"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="6"/>
+      <c r="M85" s="6"/>
+      <c r="N85" s="6"/>
+      <c r="O85" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5366,7 +5458,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="80.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="80.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5392,7 +5484,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="80.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="80.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5547,7 +5639,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$B1:$B14</xm:f>
+            <xm:f>'Select Input Data'!$B$2:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>B4:B4</xm:sqref>
         </x14:dataValidation>
@@ -5649,13 +5741,13 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$C1:$C4</xm:f>
+            <xm:f>'Select Input Data'!$C$2:$C$5</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$D1:$D4</xm:f>
+            <xm:f>'Select Input Data'!$D$2:$D$5</xm:f>
           </x14:formula1>
           <xm:sqref>H2:H2</xm:sqref>
         </x14:dataValidation>
@@ -5786,31 +5878,31 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$I1:$I31</xm:f>
+            <xm:f>'Select Input Data'!$I$2:$I$32</xm:f>
           </x14:formula1>
           <xm:sqref>B4:B4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$E1:$E84</xm:f>
+            <xm:f>'Select Input Data'!$E$2:$E$85</xm:f>
           </x14:formula1>
           <xm:sqref>B9:B9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$F1:$F2</xm:f>
+            <xm:f>'Select Input Data'!$F$2:$F$3</xm:f>
           </x14:formula1>
           <xm:sqref>B10:B10</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$G1:$G41</xm:f>
+            <xm:f>'Select Input Data'!$G$2:$G$42</xm:f>
           </x14:formula1>
           <xm:sqref>B11:B11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$H1:$H9</xm:f>
+            <xm:f>'Select Input Data'!$H$2:$H$10</xm:f>
           </x14:formula1>
           <xm:sqref>B12:B12</xm:sqref>
         </x14:dataValidation>
@@ -5922,7 +6014,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Select Input Data'!$J1:$J11</xm:f>
+            <xm:f>'Select Input Data'!$J$2:$J$12</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C2</xm:sqref>
         </x14:dataValidation>

--- a/inst/extdata/ega_full_template_v3.xlsx
+++ b/inst/extdata/ega_full_template_v3.xlsx
@@ -616,111 +616,108 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="452">
   <si>
     <t xml:space="preserve">Please read the instructions carefully to avoid submission errors</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Aliases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This sheet is not part of an actual submission, it contains placeholders that allow for internal linking of Samples, Experiments, Runs, Analyses and Datasets, so they could be translated to provisional or accession IDs during submission.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Please fill this sheet first, creating unique placeholder ID for each Sample, Experiment, Run, Analysiss and Dataset that you are submitting.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placeholders for Samples are the actual sample names.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This sheet is not a rectangular dataframe, just an enumeration of individual items. See image below for example.</t>
+    <t xml:space="preserve">Quick Instruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill the sheets in the order that they appear (apart from Collaborators, Repositories, Extra Attributes, see appropriate entry).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fields marked with * are mandatory - &gt;- Do not delete rows and columns that you don't fill in, just leave them empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Values for fields with red triangle in the corner need to be chosen from available values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fields with light green background accept multiple values separated by ; (semicolon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fields with light blue background can be present in the table multiple times and can be copied and pasted on the rows below if necessary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill in the Samples and Runs by copying the first empty row below, this will preserve the fields where you need to choose multiple values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For Studies, Experiments and Datasets, if multiple tables are needed, copy the whole table to the right (see image below)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aliases (Placeholders)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is used to create placeholder IDs that links your Samples, Experiments, Runs, Analyses and Datasets internally. These placeholder IDs will be translated to provisional or accession IDs during submission. Complete this sheet first, assigning a unique placeholder ID for each Sample, Experiment, Run, Analysis (if available) and Dataset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placeholders for Samples will become the sample names. You may choose any name (e.g. Sample1, Sample2, …), but it must be unique across all submissions under the same EGA account.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This sheet is not a rectangular dataframe. It is simply a list of individual items. See the `Aliases` sheet for an example.</t>
   </si>
   <si>
     <t xml:space="preserve">Files</t>
   </si>
   <si>
-    <t xml:space="preserve">Names of raw files for the submission, if the files were encrypted and their names differ only in the c4gh extension, there is no need to add it, it will be appended during the submission process.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If the files have been placed in the sub-directory of EGA Inbox, you can indicate it in the  'EGA Inbox Relative Path' column.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Please fill in this sheet after the Aliases as other sheets that require file names will read values from this sheet.</t>
+    <t xml:space="preserve">Names of all raw files for the submission.  If files are encrypted and differ only by the `.c4gh` extension, do not include the extension. It will be added automatically during submission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do not prefix the file names with slashes or other relative paths.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the files are located in a sub-directory within your `encrypted` EGA Inbox, specify the name of the sub-directory in the 'EGA Inbox Relative Path' name column.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete this sheet after the Aliases sheet, as other sheets depend on it.</t>
   </si>
   <si>
     <t xml:space="preserve">Analysis Files</t>
   </si>
   <si>
-    <t xml:space="preserve">Names of analysis files for the submission, if the files were encrypted and their names differ only in the c4gh extension, there is no need to add it, it will be appended during the submission process.</t>
-  </si>
-  <si>
     <t xml:space="preserve">If no analyses files are provided, leave the fields empty.</t>
   </si>
   <si>
     <t xml:space="preserve">Submission</t>
   </si>
   <si>
-    <t xml:space="preserve">The top level item that encompasses all the other. It will receive an Accession ID once completed that you can reference in your manuscript.</t>
+    <t xml:space="preserve">The top level item that encompasses all the other and will receive an Accession ID for tracking. This name and description will only be used internally during the submission process and will not be visible on the EGA webpage. For referencing in your manuscript you will only use the Study ID or the Dataset ID.</t>
   </si>
   <si>
     <t xml:space="preserve">Studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Study description is expected to be a 3-5 sentences definition of the project with some background, goals, and details.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One submission can have one or more studies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does not have to be the same as the EGA submission name.</t>
+    <t xml:space="preserve">Title is expected to be between 3 to 20 words. The title of the studies doesn’t need to match the EGA submission name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provide a 3-5 sentences as description with background, goals, and key details. One submission can include one or more studies.</t>
   </si>
   <si>
     <t xml:space="preserve">Samples</t>
   </si>
   <si>
-    <t xml:space="preserve">Summary of all biological samples linked to the submission. Please create a duplicate of the first row if you wish to add more samples.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samples need an alias which will be used to link files to samples.</t>
+    <t xml:space="preserve">List all biological samples. Duplicate the row to add additional samples. Each Subject ID must be linked to a Sample Alias to link files to samples.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Try to make the Sample names/aliases unique to not interfere with other submissions.</t>
   </si>
   <si>
     <t xml:space="preserve">Experiments</t>
   </si>
   <si>
-    <t xml:space="preserve">Here you have to specify how the experiment was done (Instrument model, design name (e.g. 'TruSeq Rna-Seq'), library type, ...).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You could create more experiments if you have different data type in to the same study/EGA submission (e.g. ATAC-seq and RNA-seq).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One submission can have one or more experiments.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform: The platform in sequencing refers to the specific technology or machine used to perform sequencing (e.g. Illumina Sequencing, Pacific Biosciences (PacBio) Sequencing, Oxford Nanopore Technologies (ONT) Sequencing, …)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instrument mode: The sequencing model refers to the specific instrument version within a platform family (e.g., Illumina NovaSeq 6000, PacBio Sequel II, ...) tailored to different scales, throughput levels, and application types. Each platform offers several models designed to address a range of project needs.  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Library Selection: Library Selection in sequencing refers to the process of enriching or selecting specific fragments of DNA or RNA that are most relevant for sequencing from a larger pool of nucleic acids. This step is crucial because it determines the portion of the genome, transcriptome, or other DNA/RNA content that will be represented in the final sequencing output.</t>
+    <t xml:space="preserve">Specify how the experiment was performed (e.g., instrument model, design name, library type) You can create more experiments if you have different data types in the same study/EGA submission (e.g. ATAC-seq and RNA-seq).</t>
   </si>
   <si>
     <t xml:space="preserve">Runs</t>
   </si>
   <si>
-    <t xml:space="preserve">Runs connect samples to files and experiment. Please create a duplicate of the first row if you wish to add more runs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Files cannot be reused among the different Runs. Each file can only be associated to one Run.</t>
+    <t xml:space="preserve">Runs connect samples to files and experiment. Duplicate the first row to add more runs. Files cannot be reused among the different Runs. Each file can only be associated to one Run.</t>
   </si>
   <si>
     <t xml:space="preserve">Analyses</t>
   </si>
   <si>
-    <t xml:space="preserve">Analyses gather processed files, for example BAM or VCF files including mapping info. They linked to one study and to one/multiple samples, files and experiments.</t>
+    <t xml:space="preserve">Analyses gather processed files, for example BAM or VCF files including mapping info. They are linked to one study and to one/multiple samples, files and experiments.</t>
   </si>
   <si>
     <t xml:space="preserve">Currently this is the only sheet/entry that is optional for the EGA submission. If you don't want to submit any analyses, delete the entries in the Alias sheet. There is not need to delete 'Analysis Files' and 'Analyses' sheets, you can leave them empty.</t>
@@ -729,58 +726,43 @@
     <t xml:space="preserve">Analysis files cannot be reused among the different Analyses</t>
   </si>
   <si>
-    <t xml:space="preserve">SEQUENCE VARIATION Analysis type must have 'Chromosomes groups' or 'Chromosomes' specified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAMPLE PHENOTYPE Analysis type cannot have 'Experiment Types', 'Genome ID', 'Chromosome groups' and 'Chromosomes' specified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selected 'Chromosome groups' and 'Chromosomes' must match 'Genome ID' (and possibly some other hidden requirement), this is not entirely clear how it is decided, spedifying 'Chromosomes' from group 3 worked for GRCh38.p14</t>
+    <t xml:space="preserve">There are three types of analyses: REFERENCE ALIGNMENT, SEQUENCE VARIATION and SAMPLE PHENOTYPE and they have specific requirements for which other fields must or cannot be specified. See the entry at the end of the Instructions sheet for details.</t>
   </si>
   <si>
     <t xml:space="preserve">Datasets</t>
   </si>
   <si>
-    <t xml:space="preserve">Here you describe your dataset(s).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For each dataset, you need to link to a policy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dataset description is expected to be a 3-4 sentences (at least 50 characters), definition of the dataset content, including sample number and details, file type, and technology/experimentation used.</t>
+    <t xml:space="preserve">For each dataset, you need to a Policy Accesion ID, this will be usually issued by your institution or a commitee that controls data access.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title is expected to be between 3 to 20 words.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description is expected to be a 3-4 sentences (at least 50 characters), definition of the dataset content, including sample number and details, file type, and technology/experimentation used.</t>
   </si>
   <si>
     <t xml:space="preserve">Collaborators, Repositories, Extra Attributes</t>
   </si>
   <si>
-    <t xml:space="preserve">These fields are present in other sheets, but for submission they are formatted as key value pairs. </t>
+    <t xml:space="preserve">These fields are present in other sheets, but for submission they are formatted as key value pairs.</t>
   </si>
   <si>
     <t xml:space="preserve">If you wish to add any of these to your submission, please create an appropriate entry in one of these 3 sheets and you will be able to select in from a dropdown menu afterwards.</t>
   </si>
   <si>
-    <t xml:space="preserve">Additional Instructions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fill in the Samples and Runs by copying the first empty row below, this will preserve the fields where you need to choose multiple values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For Studies, Experiments and Datasets, if multiple tables are needed, copy the whole table to the right (see image below)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fields marked with * are mandatory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Values for fields with red triangle in the corner need to be chosen from available values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fields with light green background accept multiple values separated by ; (semicolon)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fields with light blue background can be present in the table multiple times and can be copied and pasted on the rows below if necessary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do not delete rows and columns that you don't fill in, just leave them empty</t>
+    <t xml:space="preserve">Additional requirements for Analyses sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REFERENCE ALIGNMENT Analysis type must have 'Experiment Types', 'Genome ID', 'Chromosomes groups' or 'Chromosomes' specified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUENCE VARIATION Analysis type must have 'Experiment Types', 'Genome ID', 'Chromosomes groups' or 'Chromosomes' specified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE PHENOTYPE Analysis type cannot have 'Experiment Types', 'Platform', 'Genome ID', 'Chromosome groups' and 'Chromosomes' specified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selected 'Chromosome groups' and 'Chromosomes' must match 'Genome ID'</t>
   </si>
   <si>
     <t xml:space="preserve">Study1</t>
@@ -2004,14 +1986,14 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <b/>
     </font>
     <font>
       <sz val="16"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <b/>
     </font>
@@ -2022,12 +2004,22 @@
       <b/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2096,22 +2088,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2124,12 +2125,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:oneCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
     <xdr:from xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-      <xdr:col xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:col>
+      <xdr:col xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">2</xdr:col>
       <xdr:colOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:colOff>
-      <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">7</xdr:row>
+      <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">2</xdr:row>
       <xdr:rowOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="8267700" cy="2006600"/>
+    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="13335000" cy="1930400"/>
     <xdr:pic xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
       <xdr:nvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
         <xdr:cNvPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="1" name="Picture 1"/>
@@ -2139,36 +2140,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-        </a:blip>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-    <xdr:from xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-      <xdr:col xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:col>
-      <xdr:colOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:colOff>
-      <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">77</xdr:row>
-      <xdr:rowOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="13335000" cy="1930400"/>
-    <xdr:pic xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-      <xdr:nvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <xdr:cNvPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="2" name="Picture 2"/>
-        <xdr:cNvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
         </a:blip>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -2469,385 +2440,273 @@
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="100.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
+    <row r="3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s">
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s">
+    <row r="6">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="s">
+    <row r="7">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s">
+    <row r="8">
+      <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>1</v>
+      <c r="A9" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>1</v>
+      <c r="A10" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
-        <v>1</v>
+      <c r="A12" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>1</v>
+      <c r="A13" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s">
-        <v>1</v>
+      <c r="A14" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>1</v>
+      <c r="A15" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="s">
-        <v>7</v>
+      <c r="A17" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s">
-        <v>8</v>
+      <c r="A18" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s">
-        <v>9</v>
+      <c r="A19" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s">
-        <v>10</v>
+      <c r="A20" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="s">
-        <v>11</v>
+      <c r="A21" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s">
-        <v>12</v>
+      <c r="A23" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s">
-        <v>9</v>
+      <c r="A24" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s">
-        <v>10</v>
+      <c r="A25" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s">
-        <v>13</v>
+      <c r="A26" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s">
-        <v>1</v>
+      <c r="A27" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
+      <c r="A28" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s">
-        <v>1</v>
+      <c r="A30" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>17</v>
+      <c r="A31" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s">
-        <v>18</v>
+      <c r="A33" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s">
-        <v>19</v>
+      <c r="A34" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="s">
-        <v>20</v>
+      <c r="A35" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s">
-        <v>21</v>
+      <c r="A37" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s">
-        <v>22</v>
+      <c r="A38" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="s">
-        <v>23</v>
+      <c r="A39" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
-        <v>24</v>
+      <c r="A41" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>26</v>
+      <c r="A42" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
-        <v>27</v>
+      <c r="A44" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>29</v>
+      <c r="A45" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
-        <v>1</v>
+      <c r="A47" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="s">
-        <v>30</v>
+      <c r="A48" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
-        <v>31</v>
+      <c r="A49" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s">
-        <v>32</v>
+      <c r="A50" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="s">
-        <v>33</v>
+      <c r="A51" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s">
-        <v>34</v>
+      <c r="A53" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s">
-        <v>35</v>
+      <c r="A54" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s">
-        <v>36</v>
+      <c r="A55" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>38</v>
+      <c r="A56" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s">
-        <v>39</v>
+      <c r="A58" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s">
-        <v>1</v>
+      <c r="A59" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>41</v>
+      <c r="A60" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s">
-        <v>42</v>
+      <c r="A62" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s">
-        <v>43</v>
+      <c r="A63" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s">
-        <v>1</v>
+      <c r="A64" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="s">
-        <v>44</v>
+      <c r="A65" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
+      <c r="A66" s="2" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2870,95 +2729,95 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="7"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="7"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="7"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="7"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="7"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="7"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="6"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="6"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="s">
+      <c r="B11" s="7"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="7"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="6"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" s="6"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="6"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" s="6"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="6"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="6"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="6"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>58</v>
+      <c r="B14" s="7" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -3053,56 +2912,56 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="6"/>
+      <c r="B2" s="7"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="6"/>
+      <c r="A3" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="7"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="6"/>
+      <c r="A4" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="7"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="6"/>
+      <c r="A5" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="7"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="6"/>
+      <c r="A6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="7"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="7" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3125,13 +2984,13 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Aliases'!$E$2:$E$1000</xm:f>
+            <xm:f>'Aliases'!$F$2:$F$1000</xm:f>
           </x14:formula1>
           <xm:sqref>B7:B7</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Aliases'!$F$2:$F$100</xm:f>
+            <xm:f>'Aliases'!$E$2:$E$100</xm:f>
           </x14:formula1>
           <xm:sqref>B8:B8</xm:sqref>
         </x14:dataValidation>
@@ -3161,14 +3020,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>110</v>
+      <c r="A1" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3191,14 +3050,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>113</v>
+      <c r="A1" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -3221,14 +3080,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>116</v>
+      <c r="A1" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -3243,2143 +3102,2143 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="L1" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="M1" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="N1" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="O1" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="J1" s="6" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="L2" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="M2" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="N2" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="O2" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="O2" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="J3" s="6" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="F4" s="7"/>
+      <c r="G4" s="7" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="J4" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="L4" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="M4" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="N4" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6" t="s">
+      <c r="O4" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="H4" s="6" t="s">
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="J4" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="K4" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="L4" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="M4" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="K5" s="7"/>
+      <c r="L5" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="H5" s="6" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="M5" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="I6" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="J6" s="7" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6" t="s">
+      <c r="K6" s="7"/>
+      <c r="L6" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6" t="s">
+      <c r="M6" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6" t="s">
+      <c r="N6" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="O6" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="I6" s="6" t="s">
+    </row>
+    <row r="7">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6" t="s">
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="H7" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="I7" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="J7" s="7" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6" t="s">
+      <c r="K7" s="7"/>
+      <c r="L7" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6" t="s">
+      <c r="M7" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
+      <c r="N7" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="O7" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="I7" s="6" t="s">
+    </row>
+    <row r="8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6" t="s">
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="H8" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="I8" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="J8" s="7" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6" t="s">
+      <c r="K8" s="7"/>
+      <c r="L8" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6" t="s">
+      <c r="M8" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6" t="s">
+      <c r="N8" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="O8" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="I8" s="6" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6" t="s">
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="H9" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="I9" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="J9" s="7" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6" t="s">
+      <c r="K9" s="7"/>
+      <c r="L9" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6" t="s">
+      <c r="M9" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6" t="s">
+      <c r="N9" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="O9" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="I9" s="6" t="s">
+    </row>
+    <row r="10">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6" t="s">
+      <c r="F10" s="7"/>
+      <c r="G10" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="H10" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="I10" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="J10" s="7" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6" t="s">
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6" t="s">
+      <c r="N10" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6" t="s">
+      <c r="O10" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="H10" s="6" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="F11" s="7"/>
+      <c r="G11" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6" t="s">
+      <c r="H11" s="7"/>
+      <c r="I11" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="J11" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="O10" s="6" t="s">
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
+      <c r="N11" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6" t="s">
+      <c r="O11" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6" t="s">
+    </row>
+    <row r="12">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6" t="s">
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6" t="s">
+      <c r="H12" s="7"/>
+      <c r="I12" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="J12" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="O11" s="6" t="s">
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6" t="s">
+      <c r="N12" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6" t="s">
+      <c r="O12" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="F13" s="7"/>
+      <c r="G13" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6" t="s">
+      <c r="H13" s="7"/>
+      <c r="I13" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="O12" s="6" t="s">
+      <c r="N13" s="7" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6" t="s">
+      <c r="O13" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6" t="s">
+    </row>
+    <row r="14">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6" t="s">
+      <c r="F14" s="7"/>
+      <c r="G14" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6" t="s">
+      <c r="H14" s="7"/>
+      <c r="I14" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="N13" s="6" t="s">
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="O13" s="6" t="s">
+      <c r="N14" s="7" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6" t="s">
+      <c r="O14" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6" t="s">
+    </row>
+    <row r="15">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6" t="s">
+      <c r="F15" s="7"/>
+      <c r="G15" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6" t="s">
+      <c r="H15" s="7"/>
+      <c r="I15" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="N14" s="6" t="s">
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="O14" s="6" t="s">
+      <c r="N15" s="7" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6" t="s">
+      <c r="O15" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6" t="s">
+    </row>
+    <row r="16">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6" t="s">
+      <c r="F16" s="7"/>
+      <c r="G16" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6" t="s">
+      <c r="H16" s="7"/>
+      <c r="I16" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6" t="s">
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="N15" s="6" t="s">
+      <c r="N16" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="O15" s="6" t="s">
+      <c r="O16" s="7"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6" t="s">
+      <c r="F17" s="7"/>
+      <c r="G17" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6" t="s">
+      <c r="H17" s="7"/>
+      <c r="I17" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6" t="s">
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6" t="s">
+      <c r="N17" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="N16" s="6" t="s">
+      <c r="O17" s="7"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="O16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6" t="s">
+      <c r="F18" s="7"/>
+      <c r="G18" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6" t="s">
+      <c r="H18" s="7"/>
+      <c r="I18" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6" t="s">
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6" t="s">
+      <c r="N18" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="N17" s="6" t="s">
+      <c r="O18" s="7"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="O17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6" t="s">
+      <c r="F19" s="7"/>
+      <c r="G19" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6" t="s">
+      <c r="H19" s="7"/>
+      <c r="I19" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6" t="s">
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6" t="s">
+      <c r="N19" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="N18" s="6" t="s">
+      <c r="O19" s="7"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="O18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6" t="s">
+      <c r="F20" s="7"/>
+      <c r="G20" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6" t="s">
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6" t="s">
+      <c r="N20" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6" t="s">
+      <c r="O20" s="7"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="N19" s="6" t="s">
+      <c r="F21" s="7"/>
+      <c r="G21" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="O19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6" t="s">
+      <c r="H21" s="7"/>
+      <c r="I21" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6" t="s">
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6" t="s">
+      <c r="N21" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="N20" s="6" t="s">
+      <c r="O21" s="7"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="O20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6" t="s">
+      <c r="F22" s="7"/>
+      <c r="G22" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6" t="s">
+      <c r="H22" s="7"/>
+      <c r="I22" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6" t="s">
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6" t="s">
+      <c r="N22" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="N21" s="6" t="s">
+      <c r="O22" s="7"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="O21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6" t="s">
+      <c r="F23" s="7"/>
+      <c r="G23" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6" t="s">
+      <c r="H23" s="7"/>
+      <c r="I23" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6" t="s">
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6" t="s">
+      <c r="N23" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="N22" s="6" t="s">
+      <c r="O23" s="7"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="O22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6" t="s">
+      <c r="F24" s="7"/>
+      <c r="G24" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6" t="s">
+      <c r="H24" s="7"/>
+      <c r="I24" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6" t="s">
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6" t="s">
+      <c r="N24" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="N23" s="6" t="s">
+      <c r="O24" s="7"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="O23" s="6"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6" t="s">
+      <c r="F25" s="7"/>
+      <c r="G25" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6" t="s">
+      <c r="H25" s="7"/>
+      <c r="I25" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6" t="s">
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6" t="s">
+      <c r="N25" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="N24" s="6" t="s">
+      <c r="O25" s="7"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="O24" s="6"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6" t="s">
+      <c r="F26" s="7"/>
+      <c r="G26" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6" t="s">
+      <c r="H26" s="7"/>
+      <c r="I26" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6" t="s">
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6" t="s">
+      <c r="N26" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="N25" s="6" t="s">
+      <c r="O26" s="7"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="O25" s="6"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6" t="s">
+      <c r="F27" s="7"/>
+      <c r="G27" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6" t="s">
+      <c r="H27" s="7"/>
+      <c r="I27" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6" t="s">
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6" t="s">
+      <c r="N27" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="N26" s="6" t="s">
+      <c r="O27" s="7"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="O26" s="6"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6" t="s">
+      <c r="F28" s="7"/>
+      <c r="G28" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6" t="s">
+      <c r="H28" s="7"/>
+      <c r="I28" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6" t="s">
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6" t="s">
+      <c r="N28" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="N27" s="6" t="s">
+      <c r="O28" s="7"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="O27" s="6"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6" t="s">
+      <c r="F29" s="7"/>
+      <c r="G29" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6" t="s">
+      <c r="H29" s="7"/>
+      <c r="I29" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6" t="s">
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6" t="s">
+      <c r="N29" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="N28" s="6" t="s">
+      <c r="O29" s="7"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="O28" s="6"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6" t="s">
+      <c r="F30" s="7"/>
+      <c r="G30" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6" t="s">
+      <c r="H30" s="7"/>
+      <c r="I30" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6" t="s">
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6" t="s">
+      <c r="N30" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="N29" s="6" t="s">
+      <c r="O30" s="7"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="O29" s="6"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6" t="s">
+      <c r="F31" s="7"/>
+      <c r="G31" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6" t="s">
+      <c r="H31" s="7"/>
+      <c r="I31" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6" t="s">
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6" t="s">
+      <c r="O31" s="7"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="N30" s="6" t="s">
+      <c r="F32" s="7"/>
+      <c r="G32" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="O30" s="6"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6" t="s">
+      <c r="H32" s="7"/>
+      <c r="I32" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6" t="s">
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6" t="s">
+      <c r="O32" s="7"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6" t="s">
+      <c r="F33" s="7"/>
+      <c r="G33" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="O31" s="6"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6" t="s">
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6" t="s">
+      <c r="O33" s="7"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6" t="s">
+      <c r="F34" s="7"/>
+      <c r="G34" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6" t="s">
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="O32" s="6"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6" t="s">
+      <c r="O34" s="7"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6" t="s">
+      <c r="F35" s="7"/>
+      <c r="G35" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6" t="s">
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="O33" s="6"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6" t="s">
+      <c r="O35" s="7"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6" t="s">
+      <c r="F36" s="7"/>
+      <c r="G36" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="6" t="s">
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="O34" s="6"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6" t="s">
+      <c r="O36" s="7"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6" t="s">
+      <c r="F37" s="7"/>
+      <c r="G37" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6" t="s">
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="O35" s="6"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6" t="s">
+      <c r="O37" s="7"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6" t="s">
+      <c r="F38" s="7"/>
+      <c r="G38" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6" t="s">
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="O36" s="6"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6" t="s">
+      <c r="O38" s="7"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6" t="s">
+      <c r="F39" s="7"/>
+      <c r="G39" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6" t="s">
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="O37" s="6"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6" t="s">
+      <c r="O39" s="7"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6" t="s">
+      <c r="F40" s="7"/>
+      <c r="G40" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6" t="s">
+      <c r="O40" s="7"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="O38" s="6"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6" t="s">
+      <c r="F41" s="7"/>
+      <c r="G41" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6" t="s">
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6" t="s">
+      <c r="O41" s="7"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="O39" s="6"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6" t="s">
+      <c r="F42" s="7"/>
+      <c r="G42" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="6"/>
-      <c r="N40" s="6" t="s">
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="O40" s="6"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6" t="s">
+      <c r="O42" s="7"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6" t="s">
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7"/>
+      <c r="N43" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="6" t="s">
+      <c r="O43" s="7"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="O41" s="6"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6" t="s">
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7"/>
+      <c r="N44" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6" t="s">
+      <c r="O44" s="7"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="6"/>
-      <c r="N42" s="6" t="s">
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="O42" s="6"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6" t="s">
+      <c r="O45" s="7"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="6"/>
-      <c r="N43" s="6" t="s">
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="O43" s="6"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6" t="s">
+      <c r="O46" s="7"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="6" t="s">
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="O44" s="6"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6" t="s">
+      <c r="O47" s="7"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6" t="s">
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="O45" s="6"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6" t="s">
+      <c r="O48" s="7"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6" t="s">
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="O46" s="6"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6" t="s">
+      <c r="O49" s="7"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6" t="s">
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="O47" s="6"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6" t="s">
+      <c r="O50" s="7"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6" t="s">
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="M51" s="7"/>
+      <c r="N51" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="O48" s="6"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6" t="s">
+      <c r="O51" s="7"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6"/>
-      <c r="N49" s="6" t="s">
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="O49" s="6"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6" t="s">
+      <c r="O52" s="7"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
-      <c r="N50" s="6" t="s">
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7"/>
+      <c r="K53" s="7"/>
+      <c r="L53" s="7"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="O50" s="6"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6" t="s">
+      <c r="O53" s="7"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="6" t="s">
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
+      <c r="M54" s="7"/>
+      <c r="N54" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="O51" s="6"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6" t="s">
+      <c r="O54" s="7"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="6"/>
-      <c r="N52" s="6" t="s">
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7"/>
+      <c r="N55" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="O52" s="6"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6" t="s">
+      <c r="O55" s="7"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6" t="s">
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+      <c r="M56" s="7"/>
+      <c r="N56" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="O53" s="6"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6" t="s">
+      <c r="O56" s="7"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="6" t="s">
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="7"/>
+      <c r="M57" s="7"/>
+      <c r="N57" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="O54" s="6"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6" t="s">
+      <c r="O57" s="7"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6" t="s">
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
+      <c r="L58" s="7"/>
+      <c r="M58" s="7"/>
+      <c r="N58" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="O55" s="6"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6" t="s">
+      <c r="O58" s="7"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
-      <c r="N56" s="6" t="s">
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
+      <c r="M59" s="7"/>
+      <c r="N59" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="O56" s="6"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6" t="s">
+      <c r="O59" s="7"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
-      <c r="N57" s="6" t="s">
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+      <c r="M60" s="7"/>
+      <c r="N60" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="O57" s="6"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6" t="s">
+      <c r="O60" s="7"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
-      <c r="N58" s="6" t="s">
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
+      <c r="L61" s="7"/>
+      <c r="M61" s="7"/>
+      <c r="N61" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="O58" s="6"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6" t="s">
+      <c r="O61" s="7"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="6" t="s">
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7"/>
+      <c r="M62" s="7"/>
+      <c r="N62" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="O59" s="6"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6" t="s">
+      <c r="O62" s="7"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="6" t="s">
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
+      <c r="M63" s="7"/>
+      <c r="N63" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="O60" s="6"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6" t="s">
+      <c r="O63" s="7"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="6" t="s">
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
+      <c r="M64" s="7"/>
+      <c r="N64" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="O61" s="6"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6" t="s">
+      <c r="O64" s="7"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="6"/>
-      <c r="N62" s="6" t="s">
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7"/>
+      <c r="K65" s="7"/>
+      <c r="L65" s="7"/>
+      <c r="M65" s="7"/>
+      <c r="N65" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="O62" s="6"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6" t="s">
+      <c r="O65" s="7"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="6" t="s">
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="7"/>
+      <c r="K66" s="7"/>
+      <c r="L66" s="7"/>
+      <c r="M66" s="7"/>
+      <c r="N66" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="O63" s="6"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6" t="s">
+      <c r="O66" s="7"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
-      <c r="M64" s="6"/>
-      <c r="N64" s="6" t="s">
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+      <c r="M67" s="7"/>
+      <c r="N67" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="O64" s="6"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6" t="s">
+      <c r="O67" s="7"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="6"/>
-      <c r="N65" s="6" t="s">
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="7"/>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+      <c r="M68" s="7"/>
+      <c r="N68" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="O65" s="6"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6" t="s">
+      <c r="O68" s="7"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6"/>
-      <c r="N66" s="6" t="s">
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7"/>
+      <c r="K69" s="7"/>
+      <c r="L69" s="7"/>
+      <c r="M69" s="7"/>
+      <c r="N69" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="O66" s="6"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6" t="s">
+      <c r="O69" s="7"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
-      <c r="M67" s="6"/>
-      <c r="N67" s="6" t="s">
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="7"/>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
+      <c r="M70" s="7"/>
+      <c r="N70" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="O67" s="6"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6" t="s">
+      <c r="O70" s="7"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
-      <c r="M68" s="6"/>
-      <c r="N68" s="6" t="s">
+      <c r="F71" s="7"/>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7"/>
+      <c r="L71" s="7"/>
+      <c r="M71" s="7"/>
+      <c r="N71" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="O68" s="6"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6" t="s">
+      <c r="O71" s="7"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
-      <c r="M69" s="6"/>
-      <c r="N69" s="6" t="s">
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="7"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="7"/>
+      <c r="M72" s="7"/>
+      <c r="N72" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="O69" s="6"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6" t="s">
+      <c r="O72" s="7"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="6"/>
-      <c r="M70" s="6"/>
-      <c r="N70" s="6" t="s">
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="7"/>
+      <c r="J73" s="7"/>
+      <c r="K73" s="7"/>
+      <c r="L73" s="7"/>
+      <c r="M73" s="7"/>
+      <c r="N73" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="O70" s="6"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6" t="s">
+      <c r="O73" s="7"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
-      <c r="M71" s="6"/>
-      <c r="N71" s="6" t="s">
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="O71" s="6"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6" t="s">
+      <c r="O74" s="7"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
-      <c r="M72" s="6"/>
-      <c r="N72" s="6" t="s">
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
+      <c r="M75" s="7"/>
+      <c r="N75" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="O72" s="6"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6" t="s">
+      <c r="O75" s="7"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
-      <c r="M73" s="6"/>
-      <c r="N73" s="6" t="s">
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
+      <c r="J76" s="7"/>
+      <c r="K76" s="7"/>
+      <c r="L76" s="7"/>
+      <c r="M76" s="7"/>
+      <c r="N76" s="7"/>
+      <c r="O76" s="7"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="O73" s="6"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6" t="s">
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
+      <c r="J77" s="7"/>
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+      <c r="M77" s="7"/>
+      <c r="N77" s="7"/>
+      <c r="O77" s="7"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="6" t="s">
+      <c r="F78" s="7"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="7"/>
+      <c r="J78" s="7"/>
+      <c r="K78" s="7"/>
+      <c r="L78" s="7"/>
+      <c r="M78" s="7"/>
+      <c r="N78" s="7"/>
+      <c r="O78" s="7"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="O74" s="6"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6" t="s">
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="7"/>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
+      <c r="M79" s="7"/>
+      <c r="N79" s="7"/>
+      <c r="O79" s="7"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="6"/>
-      <c r="N75" s="6" t="s">
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="7"/>
+      <c r="K80" s="7"/>
+      <c r="L80" s="7"/>
+      <c r="M80" s="7"/>
+      <c r="N80" s="7"/>
+      <c r="O80" s="7"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="O75" s="6"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6" t="s">
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7"/>
+      <c r="L81" s="7"/>
+      <c r="M81" s="7"/>
+      <c r="N81" s="7"/>
+      <c r="O81" s="7"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7"/>
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6"/>
-      <c r="L76" s="6"/>
-      <c r="M76" s="6"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6" t="s">
+      <c r="F82" s="7"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7"/>
+      <c r="J82" s="7"/>
+      <c r="K82" s="7"/>
+      <c r="L82" s="7"/>
+      <c r="M82" s="7"/>
+      <c r="N82" s="7"/>
+      <c r="O82" s="7"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
-      <c r="M77" s="6"/>
-      <c r="N77" s="6"/>
-      <c r="O77" s="6"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6" t="s">
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="7"/>
+      <c r="K83" s="7"/>
+      <c r="L83" s="7"/>
+      <c r="M83" s="7"/>
+      <c r="N83" s="7"/>
+      <c r="O83" s="7"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
-      <c r="M78" s="6"/>
-      <c r="N78" s="6"/>
-      <c r="O78" s="6"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6" t="s">
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7"/>
+      <c r="J84" s="7"/>
+      <c r="K84" s="7"/>
+      <c r="L84" s="7"/>
+      <c r="M84" s="7"/>
+      <c r="N84" s="7"/>
+      <c r="O84" s="7"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
-      <c r="M79" s="6"/>
-      <c r="N79" s="6"/>
-      <c r="O79" s="6"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
-      <c r="M80" s="6"/>
-      <c r="N80" s="6"/>
-      <c r="O80" s="6"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6" t="s">
-        <v>453</v>
-      </c>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
-      <c r="M81" s="6"/>
-      <c r="N81" s="6"/>
-      <c r="O81" s="6"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
-      <c r="M82" s="6"/>
-      <c r="N82" s="6"/>
-      <c r="O82" s="6"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
-      <c r="M83" s="6"/>
-      <c r="N83" s="6"/>
-      <c r="O83" s="6"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
-      <c r="M84" s="6"/>
-      <c r="N84" s="6"/>
-      <c r="O84" s="6"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
-      <c r="M85" s="6"/>
-      <c r="N85" s="6"/>
-      <c r="O85" s="6"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="7"/>
+      <c r="K85" s="7"/>
+      <c r="L85" s="7"/>
+      <c r="M85" s="7"/>
+      <c r="N85" s="7"/>
+      <c r="O85" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5404,43 +5263,43 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="A1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>33</v>
+      <c r="F1" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>60</v>
+      <c r="A2" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -5462,11 +5321,11 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>62</v>
+      <c r="A1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -5488,11 +5347,11 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>62</v>
+      <c r="A1" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -5514,22 +5373,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="6"/>
+      <c r="A1" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="7"/>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="6"/>
+      <c r="A2" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="7"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="6"/>
+      <c r="A3" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5563,54 +5422,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="7"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="7"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="7"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="7"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="7"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="6"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="6"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="6"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="6"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="6"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="6"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5671,54 +5530,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="J1" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>72</v>
+      <c r="K1" s="13" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="A2" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5770,86 +5629,86 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="7"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="7"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="7"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="7"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="7"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="7"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="7"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="7"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="6"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" s="6"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="6"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="6"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="6"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="6"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="6"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="6"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="6"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B13" s="6"/>
+      <c r="B13" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5930,44 +5789,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>7</v>
+      <c r="A1" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="A2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
